--- a/Result/profitability/6224.xlsx
+++ b/Result/profitability/6224.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3975</v>
+        <v>0.3725000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>31.48</v>
+        <v>31.905</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3525</v>
+        <v>0.3775000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>32.59375</v>
+        <v>32.67625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0.425</v>
+        <v>0.46375</v>
       </c>
       <c r="N4" t="n">
-        <v>34.2725</v>
+        <v>34.7</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3975</v>
+        <v>0.4400000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>35.45375</v>
+        <v>35.9375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>0.39</v>
+        <v>0.465</v>
       </c>
       <c r="N6" t="n">
-        <v>36.7225</v>
+        <v>37.73875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>0.44375</v>
+        <v>0.5750000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>38.9075</v>
+        <v>40.43125000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>1.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6200000000000001</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>42.63500000000001</v>
+        <v>42.96749999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.7100000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>45.31124999999999</v>
+        <v>45.31125</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.9525</v>
       </c>
       <c r="N13" t="n">
-        <v>47.94499999999999</v>
+        <v>47.945</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6224</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>763</v>
+      </c>
+      <c r="D75" t="n">
+        <v>496</v>
+      </c>
+      <c r="E75" t="n">
+        <v>267</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>62</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.18%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>78</v>
+      </c>
+      <c r="K75" t="n">
+        <v>62</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4399999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.68875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.659999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0823019801980196</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.8499999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.869999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1243972999035678</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
